--- a/docs/modules/bsee/data/query_api_01_block_julia_2_api12.xlsx
+++ b/docs/modules/bsee/data/query_api_01_block_julia_2_api12.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07f9c9cfd5dcd705/Roy/FDAS/Mktg/1-World Oil/2025 article/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{0F9F216A-16A1-446F-9325-A8906BD2CAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
